--- a/docs/v2.0.0/ValueSet-VRM-ExtractionErrorHeaderURI-vs.xlsx
+++ b/docs/v2.0.0/ValueSet-VRM-ExtractionErrorHeaderURI-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T11:57:36-04:00</t>
+    <t>2025-08-11T16:10:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/v2.0.0/ValueSet-VRM-ExtractionErrorHeaderURI-vs.xlsx
+++ b/docs/v2.0.0/ValueSet-VRM-ExtractionErrorHeaderURI-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-11T16:10:00-04:00</t>
+    <t>2026-03-24T10:39:59-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
